--- a/NECP Scenario/Results/Regional Results/EL64_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL64_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547328564073052E-12</v>
+        <v>2.284569543580336E-12</v>
       </c>
       <c r="C2">
-        <v>8.102415053290707E-13</v>
+        <v>1.196288014764399E-12</v>
       </c>
       <c r="D2">
-        <v>1.190478780207143E-12</v>
+        <v>1.757696321556267E-12</v>
       </c>
       <c r="E2">
-        <v>1.749240806165944E-12</v>
+        <v>2.582687089306176E-12</v>
       </c>
       <c r="F2">
-        <v>2.570234237818362E-12</v>
+        <v>3.794851058121123E-12</v>
       </c>
       <c r="G2">
-        <v>3.776474866499497E-12</v>
+        <v>5.575817785816645E-12</v>
       </c>
       <c r="H2">
-        <v>2.288786228003074E-11</v>
+        <v>3.379316685392144E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.387264451207763E-08</v>
+        <v>7.94294570998196E-08</v>
       </c>
       <c r="C3">
-        <v>4.831551601832699E-08</v>
+        <v>7.219257440383922E-08</v>
       </c>
       <c r="D3">
-        <v>1.411556922966846E-07</v>
+        <v>2.119531191676168E-07</v>
       </c>
       <c r="E3">
-        <v>2.616131262078757E-07</v>
+        <v>3.774156755160199E-07</v>
       </c>
       <c r="F3">
-        <v>6.282090494135788E-07</v>
+        <v>9.543266260738305E-07</v>
       </c>
       <c r="G3">
-        <v>1.691606948038902E-06</v>
+        <v>3.349664027992835E-06</v>
       </c>
       <c r="H3">
-        <v>1.763357122615331E-05</v>
+        <v>2.835581117668465E-05</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.579174783748783E-08</v>
+        <v>6.751503853664666E-08</v>
       </c>
       <c r="C4">
-        <v>4.106818861779973E-08</v>
+        <v>6.136368824506339E-08</v>
       </c>
       <c r="D4">
-        <v>1.199823384544037E-07</v>
+        <v>1.801601512942742E-07</v>
       </c>
       <c r="E4">
-        <v>2.223711572789163E-07</v>
+        <v>3.208033241904169E-07</v>
       </c>
       <c r="F4">
-        <v>5.339776920037638E-07</v>
+        <v>8.11177632164556E-07</v>
       </c>
       <c r="G4">
-        <v>1.437865905835289E-06</v>
+        <v>2.847214423795712E-06</v>
       </c>
       <c r="H4">
-        <v>1.498853554223254E-05</v>
+        <v>2.410243950019137E-05</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.2367615000346711</v>
+        <v>0.2368119887828087</v>
       </c>
       <c r="D5">
-        <v>0.2357809169477001</v>
+        <v>0.2359291262014112</v>
       </c>
       <c r="E5">
-        <v>0.2922756968108023</v>
+        <v>0.291808626635531</v>
       </c>
       <c r="F5">
-        <v>0.321484053059752</v>
+        <v>0.3214566450065154</v>
       </c>
       <c r="G5">
-        <v>0.3431266838285638</v>
+        <v>0.3432327827315738</v>
       </c>
       <c r="H5">
-        <v>0.3656956859103987</v>
+        <v>0.3657574513820562</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.07325668825574008</v>
+        <v>0.07333454372805727</v>
       </c>
       <c r="C7">
-        <v>0.7493333327670723</v>
+        <v>0.7493333327188668</v>
       </c>
       <c r="D7">
-        <v>0.7388001258803029</v>
+        <v>0.7393036482196705</v>
       </c>
       <c r="E7">
-        <v>0.8996666670178196</v>
+        <v>0.8996666668642866</v>
       </c>
       <c r="F7">
-        <v>0.9806944449246467</v>
+        <v>0.9806944448651852</v>
       </c>
       <c r="G7">
-        <v>1.040361111409553</v>
+        <v>1.040361111194613</v>
       </c>
       <c r="H7">
-        <v>1.100027775132179</v>
+        <v>1.100027774176519</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.02561422665911763</v>
+        <v>0.02564144885045955</v>
       </c>
       <c r="C9">
-        <v>0.02524316177003978</v>
+        <v>0.02519267300412283</v>
       </c>
       <c r="D9">
-        <v>0.0225408053851915</v>
+        <v>0.02256865289214014</v>
       </c>
       <c r="E9">
-        <v>0.02229306787652701</v>
+        <v>0.02276013799610825</v>
       </c>
       <c r="F9">
-        <v>0.02141610250213335</v>
+        <v>0.02144351053160161</v>
       </c>
       <c r="G9">
-        <v>0.02063594252932981</v>
+        <v>0.02052984354682179</v>
       </c>
       <c r="H9">
-        <v>0.0189294102345695</v>
+        <v>0.01886764440250606</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>8.312682726041486E-08</v>
+        <v>1.225451209380888E-07</v>
       </c>
       <c r="D10">
-        <v>8.611541285853286E-08</v>
+        <v>1.305215671600579E-07</v>
       </c>
       <c r="E10">
-        <v>8.141295145465817E-08</v>
+        <v>1.227458210960099E-07</v>
       </c>
       <c r="F10">
-        <v>6.518094268889205E-08</v>
+        <v>9.772309516505129E-08</v>
       </c>
       <c r="G10">
-        <v>6.059180299034098E-08</v>
+        <v>9.077070013448947E-08</v>
       </c>
       <c r="H10">
-        <v>3.111265234539379E-07</v>
+        <v>4.641451658787744E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -771,25 +771,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.171182989859921</v>
+        <v>6.273071052811922</v>
       </c>
       <c r="C11">
-        <v>7.65626061166845</v>
+        <v>7.70082659606738</v>
       </c>
       <c r="D11">
-        <v>7.198443556884792</v>
+        <v>7.365325286840009</v>
       </c>
       <c r="E11">
-        <v>6.68091316425658</v>
+        <v>6.779808273531827</v>
       </c>
       <c r="F11">
-        <v>4.698397269707367</v>
+        <v>4.735587709758058</v>
       </c>
       <c r="G11">
-        <v>0.06947459214759509</v>
+        <v>0.06959983816871868</v>
       </c>
       <c r="H11">
-        <v>0.06856220643660477</v>
+        <v>0.06863394185550117</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7.738651119462978</v>
+        <v>7.738651121899659</v>
       </c>
       <c r="C14">
-        <v>7.860920816662082</v>
+        <v>7.860920815695714</v>
       </c>
       <c r="D14">
-        <v>8.639098404236904</v>
+        <v>8.639098398358636</v>
       </c>
       <c r="E14">
-        <v>10.30864304358269</v>
+        <v>10.30864302701606</v>
       </c>
       <c r="F14">
-        <v>12.47339157904659</v>
+        <v>12.47339153387191</v>
       </c>
       <c r="G14">
-        <v>14.77962681775508</v>
+        <v>14.77962665231804</v>
       </c>
       <c r="H14">
-        <v>17.97015689307106</v>
+        <v>17.85281797074435</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.54958817909075E-08</v>
+        <v>6.709290140410521E-08</v>
       </c>
       <c r="C19">
-        <v>4.451484609129133E-08</v>
+        <v>6.678200044374021E-08</v>
       </c>
       <c r="D19">
-        <v>1.029263951779246E-07</v>
+        <v>1.540448216168555E-07</v>
       </c>
       <c r="E19">
-        <v>1.887082679523645E-07</v>
+        <v>2.768555617549886E-07</v>
       </c>
       <c r="F19">
-        <v>3.906748505035042E-07</v>
+        <v>5.836850617025722E-07</v>
       </c>
       <c r="G19">
-        <v>6.16662736047489E-07</v>
+        <v>1.037145218821398E-06</v>
       </c>
       <c r="H19">
-        <v>3.714101851831399E-06</v>
+        <v>5.667628870149778E-06</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.639670543568846E-08</v>
+        <v>5.36743211256842E-08</v>
       </c>
       <c r="C21">
-        <v>3.561187687599564E-08</v>
+        <v>5.342560035739224E-08</v>
       </c>
       <c r="D21">
-        <v>8.234111614530213E-08</v>
+        <v>1.232358572958845E-07</v>
       </c>
       <c r="E21">
-        <v>1.50966614364854E-07</v>
+        <v>2.214844494063911E-07</v>
       </c>
       <c r="F21">
-        <v>3.12539880405766E-07</v>
+        <v>4.669480493644577E-07</v>
       </c>
       <c r="G21">
-        <v>4.933301888409536E-07</v>
+        <v>8.297161750595188E-07</v>
       </c>
       <c r="H21">
-        <v>2.97128148146808E-06</v>
+        <v>4.534103096122223E-06</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>11.49882864384175</v>
+        <v>11.68989698244731</v>
       </c>
       <c r="C24">
-        <v>14.25321874081647</v>
+        <v>14.34772009094749</v>
       </c>
       <c r="D24">
-        <v>13.43139904508308</v>
+        <v>13.74861056702667</v>
       </c>
       <c r="E24">
-        <v>12.47040780373678</v>
+        <v>12.65741705197113</v>
       </c>
       <c r="F24">
-        <v>8.767866402863969</v>
+        <v>8.83817633021801</v>
       </c>
       <c r="G24">
-        <v>0.1104647348649232</v>
+        <v>0.1106639425077988</v>
       </c>
       <c r="H24">
-        <v>0.1640844021920947</v>
+        <v>0.1839105958171825</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.092671622774453E-08</v>
+        <v>1.624549291008114E-08</v>
       </c>
       <c r="C25">
-        <v>8.208877167722544E-09</v>
+        <v>1.235977261661851E-08</v>
       </c>
       <c r="D25">
-        <v>1.101621194520143E-08</v>
+        <v>1.722448911745301E-08</v>
       </c>
       <c r="E25">
-        <v>1.306327485770405E-08</v>
+        <v>1.953785980837634E-08</v>
       </c>
       <c r="F25">
-        <v>1.117854827991682E-08</v>
+        <v>1.661756676108037E-08</v>
       </c>
       <c r="G25">
-        <v>1.197454175773953E-08</v>
+        <v>1.795788301471523E-08</v>
       </c>
       <c r="H25">
-        <v>0.01980934647369834</v>
+        <v>0.02689995191029029</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1161,13 +1161,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>4.039251304496534E-08</v>
+        <v>6.034446307947178E-08</v>
       </c>
       <c r="C26">
-        <v>0.0004401144381805082</v>
+        <v>0.002785391258325563</v>
       </c>
       <c r="D26">
-        <v>0.004128813163074967</v>
+        <v>0.004278839918617571</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.488814559599569E-08</v>
+        <v>2.189755900180884E-08</v>
       </c>
       <c r="D27">
-        <v>5.927289074891005E-08</v>
+        <v>8.897116697850522E-08</v>
       </c>
       <c r="E27">
-        <v>3.036959902144107E-07</v>
+        <v>4.472097256918866E-07</v>
       </c>
       <c r="F27">
-        <v>8.476968640399146</v>
+        <v>8.256267404057471</v>
       </c>
       <c r="G27">
-        <v>15.90558361257263</v>
+        <v>16.88291387556361</v>
       </c>
       <c r="H27">
-        <v>23.30603327086734</v>
+        <v>23.62957763228615</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.5273282708667255</v>
+        <v>0.856398260678319</v>
       </c>
       <c r="D30">
-        <v>4.873284189804454</v>
+        <v>4.87329591759231</v>
       </c>
       <c r="E30">
-        <v>4.873295942905219</v>
+        <v>4.873295718517822</v>
       </c>
       <c r="F30">
-        <v>4.873295805974183</v>
+        <v>4.873295488116683</v>
       </c>
       <c r="G30">
-        <v>4.873295603628757</v>
+        <v>4.873295335878338</v>
       </c>
       <c r="H30">
-        <v>4.873292808848501</v>
+        <v>4.873291167037295</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>1.249146431133052</v>
+        <v>1.249146428408092</v>
       </c>
       <c r="C31">
-        <v>1.249146336881758</v>
+        <v>1.249146282584361</v>
       </c>
       <c r="D31">
-        <v>1.249140067299235</v>
+        <v>1.249145917649659</v>
       </c>
       <c r="E31">
-        <v>1.24914594215184</v>
+        <v>1.249145720823131</v>
       </c>
       <c r="F31">
-        <v>1.249145806123839</v>
+        <v>1.249145492203967</v>
       </c>
       <c r="G31">
-        <v>1.249145605426282</v>
+        <v>1.249145341700356</v>
       </c>
       <c r="H31">
-        <v>1.249142851222028</v>
+        <v>1.249141246795569</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>6.819131693275368E-09</v>
+        <v>1.008089365678535E-08</v>
       </c>
       <c r="D32">
-        <v>2.042075686711501E-08</v>
+        <v>3.115842342458068E-08</v>
       </c>
       <c r="E32">
-        <v>4.599154400627253E-08</v>
+        <v>7.015167831873219E-08</v>
       </c>
       <c r="F32">
-        <v>1.067660388127099E-07</v>
+        <v>1.649617801772005E-07</v>
       </c>
       <c r="G32">
-        <v>3.036336042401934E-07</v>
+        <v>4.884335488891562E-07</v>
       </c>
       <c r="H32">
-        <v>0.5164255184652472</v>
+        <v>0.6337645542820737</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.03404460372591563</v>
+        <v>0.03404460128979329</v>
       </c>
       <c r="C33">
-        <v>0.03404460455489251</v>
+        <v>0.03404460235520038</v>
       </c>
       <c r="D33">
-        <v>0.03404459849340193</v>
+        <v>0.03404459361910367</v>
       </c>
       <c r="E33">
-        <v>0.03404459330513698</v>
+        <v>0.03404458569877866</v>
       </c>
       <c r="F33">
-        <v>0.03404458312176686</v>
+        <v>0.03404457028529485</v>
       </c>
       <c r="G33">
-        <v>0.03404456654322965</v>
+        <v>0.03404454722433866</v>
       </c>
       <c r="H33">
-        <v>0.03404436849296613</v>
+        <v>0.03404425522962599</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>3.471649324217425E-08</v>
+        <v>5.122063342381362E-08</v>
       </c>
       <c r="D34">
-        <v>3.391866503781406E-08</v>
+        <v>5.104988382686935E-08</v>
       </c>
       <c r="E34">
-        <v>6.944284721443257E-08</v>
+        <v>1.054333506197013E-07</v>
       </c>
       <c r="F34">
-        <v>1.248853655492067E-07</v>
+        <v>1.887116570409668E-07</v>
       </c>
       <c r="G34">
-        <v>1.562799965286362E-07</v>
+        <v>2.364891861430967E-07</v>
       </c>
       <c r="H34">
-        <v>8.53042450152998E-07</v>
+        <v>1.298957255468503E-06</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.09891676658147461</v>
+        <v>0.09891676657478382</v>
       </c>
       <c r="C35">
-        <v>0.0989167640853032</v>
+        <v>0.09891676288266397</v>
       </c>
       <c r="D35">
-        <v>0.09891676268703728</v>
+        <v>0.09891676083770953</v>
       </c>
       <c r="E35">
-        <v>0.09891676079234865</v>
+        <v>0.09891675804665967</v>
       </c>
       <c r="F35">
-        <v>0.09891675779673523</v>
+        <v>0.09891675342073723</v>
       </c>
       <c r="G35">
-        <v>0.0989167533242362</v>
+        <v>0.09891674720419789</v>
       </c>
       <c r="H35">
-        <v>0.09891671328734256</v>
+        <v>0.09891666244716751</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>7.496006893435212</v>
+        <v>8.052078859663684</v>
       </c>
       <c r="D36">
-        <v>7.172413106566566</v>
+        <v>7.721606384889995</v>
       </c>
       <c r="E36">
-        <v>10.66639228042923</v>
+        <v>12.1439330135418</v>
       </c>
       <c r="F36">
-        <v>10.96155026336782</v>
+        <v>12.45311525968314</v>
       </c>
       <c r="G36">
-        <v>11.07656796707269</v>
+        <v>12.59874968423804</v>
       </c>
       <c r="H36">
-        <v>11.08965464458461</v>
+        <v>12.609085562311</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5.324237723781169</v>
+        <v>5.324237718712884</v>
       </c>
       <c r="C37">
-        <v>5.299579690980799</v>
+        <v>5.29634135373679</v>
       </c>
       <c r="D37">
-        <v>5.059457231294205</v>
+        <v>5.064607438064838</v>
       </c>
       <c r="E37">
-        <v>5.083536375949064</v>
+        <v>5.074587840581324</v>
       </c>
       <c r="F37">
-        <v>5.2391666010033</v>
+        <v>5.223847962187789</v>
       </c>
       <c r="G37">
-        <v>5.31317833900183</v>
+        <v>5.315894438150615</v>
       </c>
       <c r="H37">
-        <v>5.324229047767512</v>
+        <v>5.324225017093524</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.002018731554575518</v>
+        <v>0.00201874179063304</v>
       </c>
       <c r="C38">
-        <v>0.05176501756136122</v>
+        <v>0.05782410461103946</v>
       </c>
       <c r="D38">
-        <v>0.6154997053994854</v>
+        <v>0.6200312585642743</v>
       </c>
       <c r="E38">
-        <v>0.6659922546570286</v>
+        <v>0.7168355223825977</v>
       </c>
       <c r="F38">
-        <v>2.006050996466447</v>
+        <v>2.021794575178482</v>
       </c>
       <c r="G38">
-        <v>3.374390911219614</v>
+        <v>3.641829348619769</v>
       </c>
       <c r="H38">
-        <v>3.116316198894931</v>
+        <v>2.9936990356247</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>9.936852630298512E-08</v>
+        <v>1.465223585039248E-07</v>
       </c>
       <c r="C40">
-        <v>9.283036210961833E-08</v>
+        <v>1.389745748475794E-07</v>
       </c>
       <c r="D40">
-        <v>2.440820874746092E-07</v>
+        <v>3.659979407844723E-07</v>
       </c>
       <c r="E40">
-        <v>4.503213941602402E-07</v>
+        <v>6.542712372710086E-07</v>
       </c>
       <c r="F40">
-        <v>1.018883899917083E-06</v>
+        <v>1.538011687776403E-06</v>
       </c>
       <c r="G40">
-        <v>2.308269684086392E-06</v>
+        <v>4.386809246814233E-06</v>
       </c>
       <c r="H40">
-        <v>2.134767307798471E-05</v>
+        <v>3.402344004683443E-05</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.21884532731763E-08</v>
+        <v>1.211893596623308E-07</v>
       </c>
       <c r="C41">
-        <v>7.668006549379537E-08</v>
+        <v>1.147892886024556E-07</v>
       </c>
       <c r="D41">
-        <v>2.023234545997058E-07</v>
+        <v>3.033960085901587E-07</v>
       </c>
       <c r="E41">
-        <v>3.733377716437703E-07</v>
+        <v>5.422877735968081E-07</v>
       </c>
       <c r="F41">
-        <v>8.465175724095297E-07</v>
+        <v>1.278125681529014E-06</v>
       </c>
       <c r="G41">
-        <v>1.931196094676243E-06</v>
+        <v>3.67693059885523E-06</v>
       </c>
       <c r="H41">
-        <v>1.795981702370062E-05</v>
+        <v>2.863654259631359E-05</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.718007302980882E-08</v>
+        <v>-2.533299884159396E-08</v>
       </c>
       <c r="C42">
-        <v>-1.615029661582295E-08</v>
+        <v>-2.418528624512382E-08</v>
       </c>
       <c r="D42">
-        <v>-4.175863287490344E-08</v>
+        <v>-6.260193219431355E-08</v>
       </c>
       <c r="E42">
-        <v>-7.698362251646982E-08</v>
+        <v>-1.119834636742005E-07</v>
       </c>
       <c r="F42">
-        <v>-1.723663275075533E-07</v>
+        <v>-2.59886006247389E-07</v>
       </c>
       <c r="G42">
-        <v>-3.77073589410149E-07</v>
+        <v>-7.09878647959003E-07</v>
       </c>
       <c r="H42">
-        <v>-3.387856054284087E-06</v>
+        <v>-5.386897450520835E-06</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-4.972515396894463</v>
+        <v>-5.074430689136523</v>
       </c>
       <c r="C43">
-        <v>-14.56833566822363</v>
+        <v>-15.49715058142346</v>
       </c>
       <c r="D43">
-        <v>-17.09869906277997</v>
+        <v>-17.82026790061245</v>
       </c>
       <c r="E43">
-        <v>-18.4477461061237</v>
+        <v>-20.01523316031049</v>
       </c>
       <c r="F43">
-        <v>-23.21239073631593</v>
+        <v>-24.50512566329683</v>
       </c>
       <c r="G43">
-        <v>-23.86867319076947</v>
+        <v>-26.37102583641228</v>
       </c>
       <c r="H43">
-        <v>-28.07736898680415</v>
+        <v>-30.04723146251394</v>
       </c>
     </row>
     <row r="44" spans="1:8">
